--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29678,19 +29678,19 @@
         <v>391.25</v>
       </c>
       <c r="D445" t="n">
-        <v>379.98</v>
+        <v>392.08</v>
       </c>
       <c r="E445" t="n">
-        <v>366.95</v>
+        <v>380.15</v>
       </c>
       <c r="F445" t="n">
-        <v>367.63</v>
+        <v>380.79</v>
       </c>
       <c r="G445" t="n">
-        <v>367.16</v>
+        <v>379.83</v>
       </c>
       <c r="H445" t="n">
-        <v>362.66</v>
+        <v>375.19</v>
       </c>
       <c r="I445" t="n">
         <v>381.96</v>
@@ -29726,6 +29726,72 @@
         <v>387.07</v>
       </c>
       <c r="T445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>390.21</v>
+      </c>
+      <c r="C446" t="n">
+        <v>408.85</v>
+      </c>
+      <c r="D446" t="n">
+        <v>405.93</v>
+      </c>
+      <c r="E446" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="F446" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="G446" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="H446" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="I446" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="J446" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="K446" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="L446" t="n">
+        <v>410.6</v>
+      </c>
+      <c r="M446" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="N446" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="O446" t="n">
+        <v>372.53</v>
+      </c>
+      <c r="P446" t="n">
+        <v>383.57</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>390.39</v>
+      </c>
+      <c r="R446" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="S446" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="T446" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29742,7 +29808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B527"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35015,6 +35081,46 @@
       </c>
       <c r="B527" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -35183,28 +35289,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.499931785386508</v>
+        <v>-1.49216951637415</v>
       </c>
       <c r="J2" t="n">
+        <v>445</v>
+      </c>
+      <c r="K2" t="n">
         <v>444</v>
       </c>
-      <c r="K2" t="n">
-        <v>443</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.585240613668778</v>
+        <v>0.5819747279486189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.851474824051518</v>
+        <v>7.872184019532089</v>
       </c>
       <c r="N2" t="n">
-        <v>100.3161904734812</v>
+        <v>100.8802380533616</v>
       </c>
       <c r="O2" t="n">
-        <v>10.01579704634041</v>
+        <v>10.04391547422426</v>
       </c>
       <c r="P2" t="n">
-        <v>411.7629959992271</v>
+        <v>411.6863311518929</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35261,28 +35367,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.214233309245475</v>
+        <v>-1.199525452834121</v>
       </c>
       <c r="J3" t="n">
+        <v>445</v>
+      </c>
+      <c r="K3" t="n">
         <v>444</v>
       </c>
-      <c r="K3" t="n">
-        <v>443</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.526997347217224</v>
+        <v>0.5137013978484365</v>
       </c>
       <c r="M3" t="n">
-        <v>7.192596022447336</v>
+        <v>7.257251657864517</v>
       </c>
       <c r="N3" t="n">
-        <v>83.90452706388717</v>
+        <v>86.58351362633478</v>
       </c>
       <c r="O3" t="n">
-        <v>9.159941433431065</v>
+        <v>9.305026256079817</v>
       </c>
       <c r="P3" t="n">
-        <v>405.6986366611893</v>
+        <v>405.5541883666694</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35339,28 +35445,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.203974267686136</v>
+        <v>-1.18432999658837</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6335976694192129</v>
+        <v>0.611141733006082</v>
       </c>
       <c r="M4" t="n">
-        <v>5.805008289001103</v>
+        <v>5.901222512541501</v>
       </c>
       <c r="N4" t="n">
-        <v>52.98125986542657</v>
+        <v>56.54976752143794</v>
       </c>
       <c r="O4" t="n">
-        <v>7.278822697760028</v>
+        <v>7.519957946786534</v>
       </c>
       <c r="P4" t="n">
-        <v>402.7116260010972</v>
+        <v>402.5179703330246</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35417,28 +35523,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.378018873530186</v>
+        <v>-1.365099216590041</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6640239886506355</v>
+        <v>0.6557251909010546</v>
       </c>
       <c r="M5" t="n">
-        <v>6.010806932270519</v>
+        <v>6.07824907536342</v>
       </c>
       <c r="N5" t="n">
-        <v>60.35043269459729</v>
+        <v>61.61024928982551</v>
       </c>
       <c r="O5" t="n">
-        <v>7.768554092918276</v>
+        <v>7.849219661203622</v>
       </c>
       <c r="P5" t="n">
-        <v>399.2660329139138</v>
+        <v>399.1380397146975</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35495,28 +35601,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.446414443450678</v>
+        <v>-1.425575418139869</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K6" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.669076959310571</v>
+        <v>0.6502232241370625</v>
       </c>
       <c r="M6" t="n">
-        <v>6.201813170088722</v>
+        <v>6.320144801920255</v>
       </c>
       <c r="N6" t="n">
-        <v>65.03313601984328</v>
+        <v>68.88048298745662</v>
       </c>
       <c r="O6" t="n">
-        <v>8.064312495175475</v>
+        <v>8.299426666189456</v>
       </c>
       <c r="P6" t="n">
-        <v>398.0150757366983</v>
+        <v>397.8083094229647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35573,28 +35679,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.421764319385228</v>
+        <v>-1.407294816660861</v>
       </c>
       <c r="J7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6294274748670265</v>
+        <v>0.6197400625728466</v>
       </c>
       <c r="M7" t="n">
-        <v>6.559538406225435</v>
+        <v>6.621314120669293</v>
       </c>
       <c r="N7" t="n">
-        <v>75.15534377512677</v>
+        <v>76.93348421692339</v>
       </c>
       <c r="O7" t="n">
-        <v>8.66921817554079</v>
+        <v>8.771173480038083</v>
       </c>
       <c r="P7" t="n">
-        <v>397.2048163154476</v>
+        <v>397.0621952290149</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35651,28 +35757,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.454946769394087</v>
+        <v>-1.442220459080972</v>
       </c>
       <c r="J8" t="n">
+        <v>445</v>
+      </c>
+      <c r="K8" t="n">
         <v>444</v>
       </c>
-      <c r="K8" t="n">
-        <v>443</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.7137681587714088</v>
+        <v>0.7059927700080363</v>
       </c>
       <c r="M8" t="n">
-        <v>5.672963134204846</v>
+        <v>5.715987898633779</v>
       </c>
       <c r="N8" t="n">
-        <v>53.84800887734553</v>
+        <v>55.08513246996377</v>
       </c>
       <c r="O8" t="n">
-        <v>7.338120255034359</v>
+        <v>7.421935897726669</v>
       </c>
       <c r="P8" t="n">
-        <v>397.3263012671615</v>
+        <v>397.2014799074618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35729,28 +35835,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.305733530325711</v>
+        <v>-1.295924963754022</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K9" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6496927998497035</v>
+        <v>0.6423830700732756</v>
       </c>
       <c r="M9" t="n">
-        <v>5.944378482506411</v>
+        <v>5.97444124303591</v>
       </c>
       <c r="N9" t="n">
-        <v>58.19197057720135</v>
+        <v>59.33336135448226</v>
       </c>
       <c r="O9" t="n">
-        <v>7.628366180067744</v>
+        <v>7.70281515775124</v>
       </c>
       <c r="P9" t="n">
-        <v>395.0858975066436</v>
+        <v>394.9895269099263</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35807,28 +35913,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.391218500850652</v>
+        <v>-1.3750805390393</v>
       </c>
       <c r="J10" t="n">
+        <v>445</v>
+      </c>
+      <c r="K10" t="n">
         <v>444</v>
       </c>
-      <c r="K10" t="n">
-        <v>443</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.6150883901333308</v>
+        <v>0.6001736417809023</v>
       </c>
       <c r="M10" t="n">
-        <v>6.584764937982337</v>
+        <v>6.655865312998577</v>
       </c>
       <c r="N10" t="n">
-        <v>76.46548717123946</v>
+        <v>79.72654130971434</v>
       </c>
       <c r="O10" t="n">
-        <v>8.74445465259209</v>
+        <v>8.928972018643263</v>
       </c>
       <c r="P10" t="n">
-        <v>394.8331246821076</v>
+        <v>394.6741046022206</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35885,28 +35991,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.256987589637054</v>
+        <v>-1.243661533246418</v>
       </c>
       <c r="J11" t="n">
+        <v>445</v>
+      </c>
+      <c r="K11" t="n">
         <v>444</v>
       </c>
-      <c r="K11" t="n">
-        <v>443</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.595189037221411</v>
+        <v>0.5829589494915204</v>
       </c>
       <c r="M11" t="n">
-        <v>6.507957234812961</v>
+        <v>6.566035247441076</v>
       </c>
       <c r="N11" t="n">
-        <v>67.84386974769689</v>
+        <v>70.03213799183919</v>
       </c>
       <c r="O11" t="n">
-        <v>8.236739023891486</v>
+        <v>8.368520657310896</v>
       </c>
       <c r="P11" t="n">
-        <v>391.5472239857006</v>
+        <v>391.4159118301391</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35963,28 +36069,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.038598304821002</v>
+        <v>-1.016859332947615</v>
       </c>
       <c r="J12" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L12" t="n">
-        <v>0.39889419990119</v>
+        <v>0.3759736245744439</v>
       </c>
       <c r="M12" t="n">
-        <v>7.527088117745041</v>
+        <v>7.636972875995014</v>
       </c>
       <c r="N12" t="n">
-        <v>102.198159739794</v>
+        <v>108.1721956610639</v>
       </c>
       <c r="O12" t="n">
-        <v>10.1093105472032</v>
+        <v>10.40058631333176</v>
       </c>
       <c r="P12" t="n">
-        <v>386.0329766657513</v>
+        <v>385.8175321603406</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36041,28 +36147,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.156599804002711</v>
+        <v>-1.146583085560116</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K13" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L13" t="n">
-        <v>0.49266358389762</v>
+        <v>0.4857376299134083</v>
       </c>
       <c r="M13" t="n">
-        <v>6.914224255140287</v>
+        <v>6.950430791663619</v>
       </c>
       <c r="N13" t="n">
-        <v>86.43469499746477</v>
+        <v>87.55070968367961</v>
       </c>
       <c r="O13" t="n">
-        <v>9.297026137290612</v>
+        <v>9.356853620939019</v>
       </c>
       <c r="P13" t="n">
-        <v>388.129252916782</v>
+        <v>388.0296382634294</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36119,28 +36225,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9294302606569022</v>
+        <v>-0.9227937511158366</v>
       </c>
       <c r="J14" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K14" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3067505291571374</v>
+        <v>0.3037303665771927</v>
       </c>
       <c r="M14" t="n">
-        <v>8.502411965650259</v>
+        <v>8.510739275380617</v>
       </c>
       <c r="N14" t="n">
-        <v>122.7111242232248</v>
+        <v>123.0089744707263</v>
       </c>
       <c r="O14" t="n">
-        <v>11.07750532490167</v>
+        <v>11.09094109941651</v>
       </c>
       <c r="P14" t="n">
-        <v>383.439805452215</v>
+        <v>383.3739577484502</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36197,28 +36303,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.090742729108357</v>
+        <v>-1.085046994926647</v>
       </c>
       <c r="J15" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K15" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L15" t="n">
-        <v>0.443499704913759</v>
+        <v>0.4409887426767726</v>
       </c>
       <c r="M15" t="n">
-        <v>7.825983603514304</v>
+        <v>7.83899028593358</v>
       </c>
       <c r="N15" t="n">
-        <v>94.37008926827438</v>
+        <v>94.58153163288146</v>
       </c>
       <c r="O15" t="n">
-        <v>9.714426862572717</v>
+        <v>9.725303678183087</v>
       </c>
       <c r="P15" t="n">
-        <v>388.1368697080467</v>
+        <v>388.0806850126108</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36275,28 +36381,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8376756300819909</v>
+        <v>-0.8292088506535515</v>
       </c>
       <c r="J16" t="n">
+        <v>445</v>
+      </c>
+      <c r="K16" t="n">
         <v>444</v>
       </c>
-      <c r="K16" t="n">
-        <v>443</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2268576495642175</v>
+        <v>0.2230638403666867</v>
       </c>
       <c r="M16" t="n">
-        <v>8.425338509192136</v>
+        <v>8.447816976262393</v>
       </c>
       <c r="N16" t="n">
-        <v>150.4610351703252</v>
+        <v>151.0620509100633</v>
       </c>
       <c r="O16" t="n">
-        <v>12.26625595568286</v>
+        <v>12.29073028383844</v>
       </c>
       <c r="P16" t="n">
-        <v>385.5987306311195</v>
+        <v>385.5151076142851</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36353,28 +36459,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.087505667301719</v>
+        <v>-1.078480548457861</v>
       </c>
       <c r="J17" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K17" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2792318651277099</v>
+        <v>0.2757268467228325</v>
       </c>
       <c r="M17" t="n">
-        <v>8.829259306874619</v>
+        <v>8.865863487696231</v>
       </c>
       <c r="N17" t="n">
-        <v>194.3355522802778</v>
+        <v>194.9814702839104</v>
       </c>
       <c r="O17" t="n">
-        <v>13.94042869786571</v>
+        <v>13.96357655774159</v>
       </c>
       <c r="P17" t="n">
-        <v>397.676578487192</v>
+        <v>397.5879999489271</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36431,28 +36537,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9040566380522064</v>
+        <v>-0.8974145103430867</v>
       </c>
       <c r="J18" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K18" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3446735412581468</v>
+        <v>0.3410857363992379</v>
       </c>
       <c r="M18" t="n">
-        <v>7.753428056579322</v>
+        <v>7.767279703403966</v>
       </c>
       <c r="N18" t="n">
-        <v>98.68242903019919</v>
+        <v>99.04591300665651</v>
       </c>
       <c r="O18" t="n">
-        <v>9.933903010911632</v>
+        <v>9.952181319020294</v>
       </c>
       <c r="P18" t="n">
-        <v>404.8048463039261</v>
+        <v>404.7395124395603</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36509,28 +36615,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.029740441729522</v>
+        <v>-1.024896676361638</v>
       </c>
       <c r="J19" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K19" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4256415671177635</v>
+        <v>0.4236701010937861</v>
       </c>
       <c r="M19" t="n">
-        <v>7.360691756291632</v>
+        <v>7.371938752360847</v>
       </c>
       <c r="N19" t="n">
-        <v>90.57481341356082</v>
+        <v>90.68151364689216</v>
       </c>
       <c r="O19" t="n">
-        <v>9.517080088638574</v>
+        <v>9.522684161878528</v>
       </c>
       <c r="P19" t="n">
-        <v>404.0379051994452</v>
+        <v>403.9903144984544</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36568,7 +36674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T445"/>
+  <dimension ref="A1:T446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81665,27 +81771,27 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>-40.97386301469198,172.1031678140261</t>
+          <t>-40.973882926116715,172.10302642724992</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>-40.97317563574244,172.10314974065057</t>
+          <t>-40.97319735735589,172.10299550214455</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>-40.97251081106321,172.1029714681333</t>
+          <t>-40.97253246670666,172.10281769852838</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>-40.97184408725002,172.10280663294887</t>
+          <t>-40.97186493644561,172.1026585902731</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>-40.97117072513296,172.10268888572557</t>
+          <t>-40.97119134388884,172.10254248035648</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -81744,6 +81850,108 @@
         </is>
       </c>
       <c r="T445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-40.975211703120124,172.10338892653135</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-40.97457645273629,172.10300079420165</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-40.97390571707896,172.1028645918723</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-40.97319747254571,172.1029946842128</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-40.97255784106597,172.10263752155788</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-40.97186750349989,172.10264036243942</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-40.97119382865845,172.1025248369262</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-40.970539613786855,172.10227108532462</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-40.969894623244,172.10195178714326</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-40.969217949966655,172.1018574099358</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-40.96858209073439,172.1014466202037</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-40.967865753670786,172.10163325067387</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-40.96718782124418,172.10155347313614</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-40.96651719843853,172.10141771565313</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-40.96586623286842,172.10113051084443</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-40.96520884252115,172.10089273622103</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-40.96455057839859,172.10066163934383</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-40.963869861074286,172.10060342025622</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T446"/>
+  <dimension ref="A1:T448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29498,7 +29498,7 @@
         <v>362.68</v>
       </c>
       <c r="J442" t="n">
-        <v>378.29</v>
+        <v>365.7</v>
       </c>
       <c r="K442" t="n">
         <v>372.34</v>
@@ -29564,7 +29564,7 @@
         <v>364.2</v>
       </c>
       <c r="J443" t="n">
-        <v>380.76</v>
+        <v>367.25</v>
       </c>
       <c r="K443" t="n">
         <v>373.97</v>
@@ -29612,7 +29612,7 @@
         <v>375.44</v>
       </c>
       <c r="D444" t="n">
-        <v>379.98</v>
+        <v>373.14</v>
       </c>
       <c r="E444" t="n">
         <v>366.95</v>
@@ -29630,7 +29630,7 @@
         <v>364.2</v>
       </c>
       <c r="J444" t="n">
-        <v>380.76</v>
+        <v>367.25</v>
       </c>
       <c r="K444" t="n">
         <v>373.97</v>
@@ -29672,52 +29672,52 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>389.19</v>
+        <v>371.96</v>
       </c>
       <c r="C445" t="n">
-        <v>391.25</v>
+        <v>375.44</v>
       </c>
       <c r="D445" t="n">
-        <v>392.08</v>
+        <v>373.14</v>
       </c>
       <c r="E445" t="n">
-        <v>380.15</v>
+        <v>366.95</v>
       </c>
       <c r="F445" t="n">
-        <v>380.79</v>
+        <v>367.63</v>
       </c>
       <c r="G445" t="n">
-        <v>379.83</v>
+        <v>367.16</v>
       </c>
       <c r="H445" t="n">
-        <v>375.19</v>
+        <v>362.66</v>
       </c>
       <c r="I445" t="n">
-        <v>381.96</v>
+        <v>364.2</v>
       </c>
       <c r="J445" t="n">
-        <v>393.89</v>
+        <v>367.25</v>
       </c>
       <c r="K445" t="n">
-        <v>387.43</v>
+        <v>373.97</v>
       </c>
       <c r="L445" t="n">
         <v>401.41</v>
       </c>
       <c r="M445" t="n">
-        <v>379.9</v>
+        <v>374.87</v>
       </c>
       <c r="N445" t="n">
-        <v>373.18</v>
+        <v>369.27</v>
       </c>
       <c r="O445" t="n">
         <v>369.67</v>
       </c>
       <c r="P445" t="n">
-        <v>381.01</v>
+        <v>376.6</v>
       </c>
       <c r="Q445" t="n">
-        <v>388.98</v>
+        <v>385.15</v>
       </c>
       <c r="R445" t="n">
         <v>395.19</v>
@@ -29738,52 +29738,52 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>390.21</v>
+        <v>370.96</v>
       </c>
       <c r="C446" t="n">
-        <v>408.85</v>
+        <v>374.84</v>
       </c>
       <c r="D446" t="n">
-        <v>405.93</v>
+        <v>372.02</v>
       </c>
       <c r="E446" t="n">
-        <v>380.22</v>
+        <v>365.56</v>
       </c>
       <c r="F446" t="n">
-        <v>396.21</v>
+        <v>367.43</v>
       </c>
       <c r="G446" t="n">
-        <v>381.39</v>
+        <v>367.48</v>
       </c>
       <c r="H446" t="n">
-        <v>376.7</v>
+        <v>363.07</v>
       </c>
       <c r="I446" t="n">
-        <v>383.84</v>
+        <v>364.32</v>
       </c>
       <c r="J446" t="n">
-        <v>396.59</v>
+        <v>367.84</v>
       </c>
       <c r="K446" t="n">
-        <v>390.09</v>
+        <v>375.66</v>
       </c>
       <c r="L446" t="n">
         <v>410.6</v>
       </c>
       <c r="M446" t="n">
-        <v>381.09</v>
+        <v>375.71</v>
       </c>
       <c r="N446" t="n">
-        <v>374.42</v>
+        <v>370.27</v>
       </c>
       <c r="O446" t="n">
         <v>372.53</v>
       </c>
       <c r="P446" t="n">
-        <v>383.57</v>
+        <v>379</v>
       </c>
       <c r="Q446" t="n">
-        <v>390.39</v>
+        <v>386.37</v>
       </c>
       <c r="R446" t="n">
         <v>396.64</v>
@@ -29792,6 +29792,138 @@
         <v>388.13</v>
       </c>
       <c r="T446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="C447" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="D447" t="n">
+        <v>370.03</v>
+      </c>
+      <c r="E447" t="n">
+        <v>359.97</v>
+      </c>
+      <c r="F447" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="G447" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="I447" t="n">
+        <v>364.83</v>
+      </c>
+      <c r="J447" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="K447" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="L447" t="n">
+        <v>417.24</v>
+      </c>
+      <c r="M447" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="N447" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="O447" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="P447" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="R447" t="n">
+        <v>400.16</v>
+      </c>
+      <c r="S447" t="n">
+        <v>392.92</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="C448" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="D448" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="E448" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="F448" t="n">
+        <v>364.71</v>
+      </c>
+      <c r="G448" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="H448" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="I448" t="n">
+        <v>366.58</v>
+      </c>
+      <c r="J448" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="K448" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="L448" t="n">
+        <v>412.43</v>
+      </c>
+      <c r="M448" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="N448" t="n">
+        <v>347.88</v>
+      </c>
+      <c r="O448" t="n">
+        <v>374.54</v>
+      </c>
+      <c r="P448" t="n">
+        <v>381.63</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="R448" t="n">
+        <v>401</v>
+      </c>
+      <c r="S448" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="T448" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29808,7 +29940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35121,6 +35253,26 @@
       </c>
       <c r="B531" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -35289,28 +35441,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.49216951637415</v>
+        <v>-1.509128836369747</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5819747279486189</v>
+        <v>0.5933545074696831</v>
       </c>
       <c r="M2" t="n">
-        <v>7.872184019532089</v>
+        <v>7.77620157592726</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8802380533616</v>
+        <v>98.96095342402612</v>
       </c>
       <c r="O2" t="n">
-        <v>10.04391547422426</v>
+        <v>9.947912013283295</v>
       </c>
       <c r="P2" t="n">
-        <v>411.6863311518929</v>
+        <v>411.8537837026168</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35367,28 +35519,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.199525452834121</v>
+        <v>-1.220981900962498</v>
       </c>
       <c r="J3" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K3" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5137013978484365</v>
+        <v>0.5354822563748824</v>
       </c>
       <c r="M3" t="n">
-        <v>7.257251657864517</v>
+        <v>7.118208340162969</v>
       </c>
       <c r="N3" t="n">
-        <v>86.58351362633478</v>
+        <v>82.62729571942015</v>
       </c>
       <c r="O3" t="n">
-        <v>9.305026256079817</v>
+        <v>9.089955760036467</v>
       </c>
       <c r="P3" t="n">
-        <v>405.5541883666694</v>
+        <v>405.7648343570602</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35445,28 +35597,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.18432999658837</v>
+        <v>-1.210078445386335</v>
       </c>
       <c r="J4" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.611141733006082</v>
+        <v>0.6408432118382462</v>
       </c>
       <c r="M4" t="n">
-        <v>5.901222512541501</v>
+        <v>5.745920487967206</v>
       </c>
       <c r="N4" t="n">
-        <v>56.54976752143794</v>
+        <v>52.26474983131993</v>
       </c>
       <c r="O4" t="n">
-        <v>7.519957946786534</v>
+        <v>7.229436342573322</v>
       </c>
       <c r="P4" t="n">
-        <v>402.5179703330246</v>
+        <v>402.77175338222</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35523,28 +35675,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.365099216590041</v>
+        <v>-1.378705703002373</v>
       </c>
       <c r="J5" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6557251909010546</v>
+        <v>0.6672558004476379</v>
       </c>
       <c r="M5" t="n">
-        <v>6.07824907536342</v>
+        <v>5.98834620876066</v>
       </c>
       <c r="N5" t="n">
-        <v>61.61024928982551</v>
+        <v>59.99594063977292</v>
       </c>
       <c r="O5" t="n">
-        <v>7.849219661203622</v>
+        <v>7.745704657406769</v>
       </c>
       <c r="P5" t="n">
-        <v>399.1380397146975</v>
+        <v>399.2729519527952</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35601,28 +35753,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.425575418139869</v>
+        <v>-1.43820851522054</v>
       </c>
       <c r="J6" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6502232241370625</v>
+        <v>0.6687102495225469</v>
       </c>
       <c r="M6" t="n">
-        <v>6.320144801920255</v>
+        <v>6.210876987636296</v>
       </c>
       <c r="N6" t="n">
-        <v>68.88048298745662</v>
+        <v>64.89443592872533</v>
       </c>
       <c r="O6" t="n">
-        <v>8.299426666189456</v>
+        <v>8.055708282250874</v>
       </c>
       <c r="P6" t="n">
-        <v>397.8083094229647</v>
+        <v>397.9333613810564</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35679,28 +35831,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.407294816660861</v>
+        <v>-1.411469294919704</v>
       </c>
       <c r="J7" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K7" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6197400625728466</v>
+        <v>0.6279482867954971</v>
       </c>
       <c r="M7" t="n">
-        <v>6.621314120669293</v>
+        <v>6.568933200595719</v>
       </c>
       <c r="N7" t="n">
-        <v>76.93348421692339</v>
+        <v>75.11362343518417</v>
       </c>
       <c r="O7" t="n">
-        <v>8.771173480038083</v>
+        <v>8.666811607228126</v>
       </c>
       <c r="P7" t="n">
-        <v>397.0621952290149</v>
+        <v>397.1029108547302</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35757,28 +35909,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.442220459080972</v>
+        <v>-1.447923155612437</v>
       </c>
       <c r="J8" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K8" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7059927700080363</v>
+        <v>0.7138748191166933</v>
       </c>
       <c r="M8" t="n">
-        <v>5.715987898633779</v>
+        <v>5.664999153546495</v>
       </c>
       <c r="N8" t="n">
-        <v>55.08513246996377</v>
+        <v>53.71103094035919</v>
       </c>
       <c r="O8" t="n">
-        <v>7.421935897726669</v>
+        <v>7.328780999617821</v>
       </c>
       <c r="P8" t="n">
-        <v>397.2014799074618</v>
+        <v>397.2570925180943</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35835,28 +35987,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.295924963754022</v>
+        <v>-1.306323860804117</v>
       </c>
       <c r="J9" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K9" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6423830700732756</v>
+        <v>0.6564656115333174</v>
       </c>
       <c r="M9" t="n">
-        <v>5.97444124303591</v>
+        <v>5.901546130500355</v>
       </c>
       <c r="N9" t="n">
-        <v>59.33336135448226</v>
+        <v>56.96493453929485</v>
       </c>
       <c r="O9" t="n">
-        <v>7.70281515775124</v>
+        <v>7.547511811139804</v>
       </c>
       <c r="P9" t="n">
-        <v>394.9895269099263</v>
+        <v>395.0912931785595</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35913,28 +36065,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3750805390393</v>
+        <v>-1.405174950577911</v>
       </c>
       <c r="J10" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K10" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6001736417809023</v>
+        <v>0.6385807756608735</v>
       </c>
       <c r="M10" t="n">
-        <v>6.655865312998577</v>
+        <v>6.46610359551157</v>
       </c>
       <c r="N10" t="n">
-        <v>79.72654130971434</v>
+        <v>71.09482309834105</v>
       </c>
       <c r="O10" t="n">
-        <v>8.928972018643263</v>
+        <v>8.431774611452861</v>
       </c>
       <c r="P10" t="n">
-        <v>394.6741046022206</v>
+        <v>394.9691978859108</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35991,28 +36143,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.243661533246418</v>
+        <v>-1.241577617607566</v>
       </c>
       <c r="J11" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K11" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5829589494915204</v>
+        <v>0.5907581778277519</v>
       </c>
       <c r="M11" t="n">
-        <v>6.566035247441076</v>
+        <v>6.547179371688752</v>
       </c>
       <c r="N11" t="n">
-        <v>70.03213799183919</v>
+        <v>67.93597099853447</v>
       </c>
       <c r="O11" t="n">
-        <v>8.368520657310896</v>
+        <v>8.242328008429078</v>
       </c>
       <c r="P11" t="n">
-        <v>391.4159118301391</v>
+        <v>391.394560060535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36069,28 +36221,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.016859332947615</v>
+        <v>-0.970296507897663</v>
       </c>
       <c r="J12" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K12" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3759736245744439</v>
+        <v>0.3285225450247126</v>
       </c>
       <c r="M12" t="n">
-        <v>7.636972875995014</v>
+        <v>7.896709351499606</v>
       </c>
       <c r="N12" t="n">
-        <v>108.1721956610639</v>
+        <v>121.9099296106745</v>
       </c>
       <c r="O12" t="n">
-        <v>10.40058631333176</v>
+        <v>11.04128296941413</v>
       </c>
       <c r="P12" t="n">
-        <v>385.8175321603406</v>
+        <v>385.3536386842903</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36147,28 +36299,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.146583085560116</v>
+        <v>-1.13731558898877</v>
       </c>
       <c r="J13" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K13" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4857376299134083</v>
+        <v>0.4833606821954448</v>
       </c>
       <c r="M13" t="n">
-        <v>6.950430791663619</v>
+        <v>6.966976829874187</v>
       </c>
       <c r="N13" t="n">
-        <v>87.55070968367961</v>
+        <v>87.40792163885229</v>
       </c>
       <c r="O13" t="n">
-        <v>9.356853620939019</v>
+        <v>9.349220375991374</v>
       </c>
       <c r="P13" t="n">
-        <v>388.0296382634294</v>
+        <v>387.9367176146787</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36225,28 +36377,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9227937511158366</v>
+        <v>-0.9235561046757613</v>
       </c>
       <c r="J14" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K14" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3037303665771927</v>
+        <v>0.3054268779959405</v>
       </c>
       <c r="M14" t="n">
-        <v>8.510739275380617</v>
+        <v>8.516733429179846</v>
       </c>
       <c r="N14" t="n">
-        <v>123.0089744707263</v>
+        <v>122.8536900228766</v>
       </c>
       <c r="O14" t="n">
-        <v>11.09094109941651</v>
+        <v>11.08393838050702</v>
       </c>
       <c r="P14" t="n">
-        <v>383.3739577484502</v>
+        <v>383.38135996609</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36303,28 +36455,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.085046994926647</v>
+        <v>-1.071200860308725</v>
       </c>
       <c r="J15" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K15" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4409887426767726</v>
+        <v>0.4337721683150123</v>
       </c>
       <c r="M15" t="n">
-        <v>7.83899028593358</v>
+        <v>7.87738828140156</v>
       </c>
       <c r="N15" t="n">
-        <v>94.58153163288146</v>
+        <v>95.41410190443061</v>
       </c>
       <c r="O15" t="n">
-        <v>9.725303678183087</v>
+        <v>9.768014225236909</v>
       </c>
       <c r="P15" t="n">
-        <v>388.0806850126108</v>
+        <v>387.9433789323813</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36381,28 +36533,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8292088506535515</v>
+        <v>-0.8174223384115781</v>
       </c>
       <c r="J16" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K16" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2230638403666867</v>
+        <v>0.2187808886920667</v>
       </c>
       <c r="M16" t="n">
-        <v>8.447816976262393</v>
+        <v>8.468135234670726</v>
       </c>
       <c r="N16" t="n">
-        <v>151.0620509100633</v>
+        <v>151.2745951558832</v>
       </c>
       <c r="O16" t="n">
-        <v>12.29073028383844</v>
+        <v>12.29937377088294</v>
       </c>
       <c r="P16" t="n">
-        <v>385.5151076142851</v>
+        <v>385.397857315937</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36459,28 +36611,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.078480548457861</v>
+        <v>-1.066454304214889</v>
       </c>
       <c r="J17" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K17" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2757268467228325</v>
+        <v>0.2722870194033392</v>
       </c>
       <c r="M17" t="n">
-        <v>8.865863487696231</v>
+        <v>8.902674986975127</v>
       </c>
       <c r="N17" t="n">
-        <v>194.9814702839104</v>
+        <v>194.9685329754712</v>
       </c>
       <c r="O17" t="n">
-        <v>13.96357655774159</v>
+        <v>13.96311329809621</v>
       </c>
       <c r="P17" t="n">
-        <v>397.5879999489271</v>
+        <v>397.4691342108062</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36537,28 +36689,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8974145103430867</v>
+        <v>-0.8809736578465124</v>
       </c>
       <c r="J18" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K18" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3410857363992379</v>
+        <v>0.3309496946332978</v>
       </c>
       <c r="M18" t="n">
-        <v>7.767279703403966</v>
+        <v>7.811441127302251</v>
       </c>
       <c r="N18" t="n">
-        <v>99.04591300665651</v>
+        <v>100.3940948559082</v>
       </c>
       <c r="O18" t="n">
-        <v>9.952181319020294</v>
+        <v>10.01968536711149</v>
       </c>
       <c r="P18" t="n">
-        <v>404.7395124395603</v>
+        <v>404.5769331418538</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36615,28 +36767,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.024896676361638</v>
+        <v>-1.010962212160989</v>
       </c>
       <c r="J19" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K19" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4236701010937861</v>
+        <v>0.4159126509521227</v>
       </c>
       <c r="M19" t="n">
-        <v>7.371938752360847</v>
+        <v>7.418729022622125</v>
       </c>
       <c r="N19" t="n">
-        <v>90.68151364689216</v>
+        <v>91.55733896121161</v>
       </c>
       <c r="O19" t="n">
-        <v>9.522684161878528</v>
+        <v>9.568559920970952</v>
       </c>
       <c r="P19" t="n">
-        <v>403.9903144984544</v>
+        <v>403.8526844631191</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36674,7 +36826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T446"/>
+  <dimension ref="A1:T448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81495,7 +81647,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>-40.96986451044127,172.10216560739758</t>
+          <t>-40.96984379325965,172.10231271094997</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -81597,7 +81749,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>-40.96986857487017,172.10213674751628</t>
+          <t>-40.96984634383627,172.10229460050948</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -81669,7 +81821,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>-40.97386301469198,172.1031678140261</t>
+          <t>-40.97385175890036,172.1032477384154</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -81699,7 +81851,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>-40.96986857487017,172.10213674751628</t>
+          <t>-40.96984634383627,172.10229460050948</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -81761,52 +81913,52 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>-40.97521002461966,172.10340084532322</t>
+          <t>-40.975181670939435,172.10360217933743</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>-40.97454749077514,172.10320644986092</t>
+          <t>-40.97452147406253,172.10339118925688</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>-40.973882926116715,172.10302642724992</t>
+          <t>-40.97385175890036,172.1032477384154</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>-40.97319735735589,172.10299550214455</t>
+          <t>-40.97317563574244,172.10314974065057</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>-40.97253246670666,172.10281769852838</t>
+          <t>-40.97251081106321,172.1029714681333</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>-40.97186493644561,172.1026585902731</t>
+          <t>-40.97184408725002,172.10280663294887</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>-40.97119134388884,172.10254248035648</t>
+          <t>-40.97117072513296,172.10268888572557</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>-40.9705365202015,172.10229305177023</t>
+          <t>-40.970507295485284,172.1025005644781</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>-40.96989018039655,172.10198333440573</t>
+          <t>-40.96984634383627,172.10229460050948</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>-40.96921357294623,172.10188848951523</t>
+          <t>-40.969191424435536,172.10204575679995</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -81816,12 +81968,12 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>-40.967863942040466,172.10164718894</t>
+          <t>-40.96785628445834,172.10170610446025</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>-40.967185935421966,172.1015679973306</t>
+          <t>-40.96717998898665,172.10161379539025</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -81831,12 +81983,12 @@
       </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>-40.96586233963301,172.1011604956946</t>
+          <t>-40.96585563290833,172.1012121492761</t>
         </is>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
-          <t>-40.96520669822604,172.10090925115585</t>
+          <t>-40.96520087363937,172.1009541108672</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
@@ -81863,52 +82015,52 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>-40.975211703120124,172.10338892653135</t>
+          <t>-40.97518002532904,172.1036138644173</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>-40.97457645273629,172.10300079420165</t>
+          <t>-40.97452048670514,172.10339820023688</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>-40.97390571707896,172.1028645918723</t>
+          <t>-40.97384991584145,172.10326082544742</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>-40.97319747254571,172.1029946842128</t>
+          <t>-40.973173348378644,172.10316598242696</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>-40.97255784106597,172.10263752155788</t>
+          <t>-40.9725104819485,172.10297380505665</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>-40.97186750349989,172.10264036243942</t>
+          <t>-40.971844613830314,172.10280289390843</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>-40.97119382865845,172.1025248369262</t>
+          <t>-40.97117139981188,172.1026840951283</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>-40.970539613786855,172.10227108532462</t>
+          <t>-40.97050749295084,172.1024991623658</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>-40.969894623244,172.10195178714326</t>
+          <t>-40.96984731470018,172.1022877068576</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>-40.969217949966655,172.1018574099358</t>
+          <t>-40.9691942053525,172.10202601076458</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -81918,12 +82070,12 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>-40.967865753670786,172.10163325067387</t>
+          <t>-40.96785756326144,172.10169626568637</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>-40.96718782124418,172.10155347313614</t>
+          <t>-40.967181509815845,172.10160208233228</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -81933,12 +82085,12 @@
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>-40.96586623286842,172.10113051084443</t>
+          <t>-40.96585928282941,172.1011840384847</t>
         </is>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
-          <t>-40.96520884252115,172.10089273622103</t>
+          <t>-40.96520272899263,172.1009398213516</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
@@ -81952,6 +82104,210 @@
         </is>
       </c>
       <c r="T446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-40.97517538470128,172.10364681633953</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-40.97451645499137,172.1034268284032</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-40.97384664111702,172.10328407829718</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-40.97316414953267,172.10323130006353</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-40.97250617054136,172.1030044187503</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-40.97184300117777,172.10281434471955</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-40.97117144917862,172.1026837445968</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-40.97050833217927,172.10249320338846</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-40.96984769317244,172.10228501950172</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-40.96919318513484,172.1020332548724</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-40.96859261324447,172.10136894179269</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-40.96785797430511,172.1016931032233</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-40.96718894665333,172.1015448054713</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-40.966523296902345,172.10137074674662</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-40.965864088548344,172.1011470259381</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-40.9652035806296,172.10093326222943</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-40.96455593146215,172.10062041096347</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>-40.963877145498145,172.10054731743963</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-40.975177540455064,172.10363150888685</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-40.97451372329553,172.10344622544454</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-40.97384214864821,172.10331597793171</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-40.973162783690114,172.10324099838732</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-40.97250600598366,172.1030055872118</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-40.97184500876547,172.10280008962806</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-40.97117510231464,172.1026578052635</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-40.97051121188233,172.102472755916</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-40.96984634383627,172.10229460050948</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-40.96919028903058,172.10205381879027</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-40.96858499076876,172.10142521184883</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-40.96785011878871,172.1017535414004</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-40.967147458164,172.1018643375767</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-40.96652025527691,172.10139417263622</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-40.96586328252668,172.101153233739</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-40.965203930408975,172.10093056830422</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-40.964557208895584,172.10061057237178</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>-40.963878453345885,172.10053724469887</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T448"/>
+  <dimension ref="A1:T449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29906,7 +29906,7 @@
         <v>370.82</v>
       </c>
       <c r="N448" t="n">
-        <v>347.88</v>
+        <v>375.16</v>
       </c>
       <c r="O448" t="n">
         <v>374.54</v>
@@ -29924,6 +29924,72 @@
         <v>393.78</v>
       </c>
       <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="C449" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="D449" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="E449" t="n">
+        <v>353.19</v>
+      </c>
+      <c r="F449" t="n">
+        <v>358.92</v>
+      </c>
+      <c r="G449" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="H449" t="n">
+        <v>362.19</v>
+      </c>
+      <c r="I449" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="J449" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="K449" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="L449" t="n">
+        <v>415.26</v>
+      </c>
+      <c r="M449" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="N449" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="O449" t="n">
+        <v>373</v>
+      </c>
+      <c r="P449" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>389.14</v>
+      </c>
+      <c r="R449" t="n">
+        <v>401.15</v>
+      </c>
+      <c r="S449" t="n">
+        <v>395.15</v>
+      </c>
+      <c r="T449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29940,7 +30006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35273,6 +35339,16 @@
       </c>
       <c r="B533" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -35441,28 +35517,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.509128836369747</v>
+        <v>-1.510373878998593</v>
       </c>
       <c r="J2" t="n">
+        <v>448</v>
+      </c>
+      <c r="K2" t="n">
         <v>447</v>
       </c>
-      <c r="K2" t="n">
-        <v>446</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5933545074696831</v>
+        <v>0.5948622027691762</v>
       </c>
       <c r="M2" t="n">
-        <v>7.77620157592726</v>
+        <v>7.766159527367391</v>
       </c>
       <c r="N2" t="n">
-        <v>98.96095342402612</v>
+        <v>98.76000109443612</v>
       </c>
       <c r="O2" t="n">
-        <v>9.947912013283295</v>
+        <v>9.937806654108146</v>
       </c>
       <c r="P2" t="n">
-        <v>411.8537837026168</v>
+        <v>411.8661823379195</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35519,28 +35595,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.220981900962498</v>
+        <v>-1.221492401643597</v>
       </c>
       <c r="J3" t="n">
+        <v>448</v>
+      </c>
+      <c r="K3" t="n">
         <v>447</v>
       </c>
-      <c r="K3" t="n">
-        <v>446</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.5354822563748824</v>
+        <v>0.5368717913733813</v>
       </c>
       <c r="M3" t="n">
-        <v>7.118208340162969</v>
+        <v>7.1050147356744</v>
       </c>
       <c r="N3" t="n">
-        <v>82.62729571942015</v>
+        <v>82.44592139240713</v>
       </c>
       <c r="O3" t="n">
-        <v>9.089955760036467</v>
+        <v>9.079973644918091</v>
       </c>
       <c r="P3" t="n">
-        <v>405.7648343570602</v>
+        <v>405.769889970282</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35597,28 +35673,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.210078445386335</v>
+        <v>-1.212075459415181</v>
       </c>
       <c r="J4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6408432118382462</v>
+        <v>0.642469695493552</v>
       </c>
       <c r="M4" t="n">
-        <v>5.745920487967206</v>
+        <v>5.744123417292807</v>
       </c>
       <c r="N4" t="n">
-        <v>52.26474983131993</v>
+        <v>52.20031247537838</v>
       </c>
       <c r="O4" t="n">
-        <v>7.229436342573322</v>
+        <v>7.224978371966132</v>
       </c>
       <c r="P4" t="n">
-        <v>402.77175338222</v>
+        <v>402.791615468685</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35675,28 +35751,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.378705703002373</v>
+        <v>-1.382315498707668</v>
       </c>
       <c r="J5" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6672558004476379</v>
+        <v>0.6688455550119289</v>
       </c>
       <c r="M5" t="n">
-        <v>5.98834620876066</v>
+        <v>5.991528793693445</v>
       </c>
       <c r="N5" t="n">
-        <v>59.99594063977292</v>
+        <v>60.03253185179508</v>
       </c>
       <c r="O5" t="n">
-        <v>7.745704657406769</v>
+        <v>7.748066329852571</v>
       </c>
       <c r="P5" t="n">
-        <v>399.2729519527952</v>
+        <v>399.3090431999083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35753,28 +35829,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.43820851522054</v>
+        <v>-1.438238785879717</v>
       </c>
       <c r="J6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6687102495225469</v>
+        <v>0.6697818220508945</v>
       </c>
       <c r="M6" t="n">
-        <v>6.210876987636296</v>
+        <v>6.196966788954569</v>
       </c>
       <c r="N6" t="n">
-        <v>64.89443592872533</v>
+        <v>64.74762803111638</v>
       </c>
       <c r="O6" t="n">
-        <v>8.055708282250874</v>
+        <v>8.046591081390702</v>
       </c>
       <c r="P6" t="n">
-        <v>397.9333613810564</v>
+        <v>397.9336644048722</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35831,28 +35907,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.411469294919704</v>
+        <v>-1.408995398459758</v>
       </c>
       <c r="J7" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6279482867954971</v>
+        <v>0.6279976613000836</v>
       </c>
       <c r="M7" t="n">
-        <v>6.568933200595719</v>
+        <v>6.567024351482107</v>
       </c>
       <c r="N7" t="n">
-        <v>75.11362343518417</v>
+        <v>75.02594973315635</v>
       </c>
       <c r="O7" t="n">
-        <v>8.666811607228126</v>
+        <v>8.661752116815416</v>
       </c>
       <c r="P7" t="n">
-        <v>397.1029108547302</v>
+        <v>397.0783042654906</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35909,28 +35985,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.447923155612437</v>
+        <v>-1.446235181823753</v>
       </c>
       <c r="J8" t="n">
+        <v>448</v>
+      </c>
+      <c r="K8" t="n">
         <v>447</v>
       </c>
-      <c r="K8" t="n">
-        <v>446</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.7138748191166933</v>
+        <v>0.7142328154492648</v>
       </c>
       <c r="M8" t="n">
-        <v>5.664999153546495</v>
+        <v>5.659551942098035</v>
       </c>
       <c r="N8" t="n">
-        <v>53.71103094035919</v>
+        <v>53.62886116013112</v>
       </c>
       <c r="O8" t="n">
-        <v>7.328780999617821</v>
+        <v>7.323172888859795</v>
       </c>
       <c r="P8" t="n">
-        <v>397.2570925180943</v>
+        <v>397.2403840007782</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35987,28 +36063,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.306323860804117</v>
+        <v>-1.303904927491234</v>
       </c>
       <c r="J9" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K9" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6564656115333174</v>
+        <v>0.6564032560402631</v>
       </c>
       <c r="M9" t="n">
-        <v>5.901546130500355</v>
+        <v>5.898783302624808</v>
       </c>
       <c r="N9" t="n">
-        <v>56.96493453929485</v>
+        <v>56.91558136095199</v>
       </c>
       <c r="O9" t="n">
-        <v>7.547511811139804</v>
+        <v>7.544241602769094</v>
       </c>
       <c r="P9" t="n">
-        <v>395.0912931785595</v>
+        <v>395.067328904423</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36065,28 +36141,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.405174950577911</v>
+        <v>-1.401061957640661</v>
       </c>
       <c r="J10" t="n">
+        <v>448</v>
+      </c>
+      <c r="K10" t="n">
         <v>447</v>
       </c>
-      <c r="K10" t="n">
-        <v>446</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.6385807756608735</v>
+        <v>0.6376065490533515</v>
       </c>
       <c r="M10" t="n">
-        <v>6.46610359551157</v>
+        <v>6.472752686951506</v>
       </c>
       <c r="N10" t="n">
-        <v>71.09482309834105</v>
+        <v>71.16001471625513</v>
       </c>
       <c r="O10" t="n">
-        <v>8.431774611452861</v>
+        <v>8.435639555852012</v>
       </c>
       <c r="P10" t="n">
-        <v>394.9691978859108</v>
+        <v>394.9283321911794</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36143,28 +36219,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.241577617607566</v>
+        <v>-1.23517615235825</v>
       </c>
       <c r="J11" t="n">
+        <v>448</v>
+      </c>
+      <c r="K11" t="n">
         <v>447</v>
       </c>
-      <c r="K11" t="n">
-        <v>446</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.5907581778277519</v>
+        <v>0.587485560455032</v>
       </c>
       <c r="M11" t="n">
-        <v>6.547179371688752</v>
+        <v>6.56692212060986</v>
       </c>
       <c r="N11" t="n">
-        <v>67.93597099853447</v>
+        <v>68.32718524701778</v>
       </c>
       <c r="O11" t="n">
-        <v>8.242328008429078</v>
+        <v>8.266025964574379</v>
       </c>
       <c r="P11" t="n">
-        <v>391.394560060535</v>
+        <v>391.3309566630327</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36221,28 +36297,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.970296507897663</v>
+        <v>-0.9471779638133379</v>
       </c>
       <c r="J12" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K12" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3285225450247126</v>
+        <v>0.3068907387349067</v>
       </c>
       <c r="M12" t="n">
-        <v>7.896709351499606</v>
+        <v>8.034572006031668</v>
       </c>
       <c r="N12" t="n">
-        <v>121.9099296106745</v>
+        <v>128.6915517577939</v>
       </c>
       <c r="O12" t="n">
-        <v>11.04128296941413</v>
+        <v>11.34422988826451</v>
       </c>
       <c r="P12" t="n">
-        <v>385.3536386842903</v>
+        <v>385.1226136896018</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36299,28 +36375,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.13731558898877</v>
+        <v>-1.132830104365897</v>
       </c>
       <c r="J13" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K13" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4833606821954448</v>
+        <v>0.4818300539664815</v>
       </c>
       <c r="M13" t="n">
-        <v>6.966976829874187</v>
+        <v>6.975026321644766</v>
       </c>
       <c r="N13" t="n">
-        <v>87.40792163885229</v>
+        <v>87.47448561981508</v>
       </c>
       <c r="O13" t="n">
-        <v>9.349220375991374</v>
+        <v>9.352779566514711</v>
       </c>
       <c r="P13" t="n">
-        <v>387.9367176146787</v>
+        <v>387.8917378635026</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36377,28 +36453,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9235561046757613</v>
+        <v>-0.9067398344716945</v>
       </c>
       <c r="J14" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K14" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3054268779959405</v>
+        <v>0.2973786609539513</v>
       </c>
       <c r="M14" t="n">
-        <v>8.516733429179846</v>
+        <v>8.519084370872909</v>
       </c>
       <c r="N14" t="n">
-        <v>122.8536900228766</v>
+        <v>123.3478034962874</v>
       </c>
       <c r="O14" t="n">
-        <v>11.08393838050702</v>
+        <v>11.10620563001997</v>
       </c>
       <c r="P14" t="n">
-        <v>383.38135996609</v>
+        <v>383.2134513864346</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36455,28 +36531,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.071200860308725</v>
+        <v>-1.065405728041774</v>
       </c>
       <c r="J15" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K15" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4337721683150123</v>
+        <v>0.4311505485447825</v>
       </c>
       <c r="M15" t="n">
-        <v>7.87738828140156</v>
+        <v>7.890277249071482</v>
       </c>
       <c r="N15" t="n">
-        <v>95.41410190443061</v>
+        <v>95.6421357272942</v>
       </c>
       <c r="O15" t="n">
-        <v>9.768014225236909</v>
+        <v>9.779679735415378</v>
       </c>
       <c r="P15" t="n">
-        <v>387.9433789323813</v>
+        <v>387.8857353463122</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36533,28 +36609,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8174223384115781</v>
+        <v>-0.8098219823880802</v>
       </c>
       <c r="J16" t="n">
+        <v>448</v>
+      </c>
+      <c r="K16" t="n">
         <v>447</v>
       </c>
-      <c r="K16" t="n">
-        <v>446</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.2187808886920667</v>
+        <v>0.215566739630635</v>
       </c>
       <c r="M16" t="n">
-        <v>8.468135234670726</v>
+        <v>8.487123011187359</v>
       </c>
       <c r="N16" t="n">
-        <v>151.2745951558832</v>
+        <v>151.6977486632324</v>
       </c>
       <c r="O16" t="n">
-        <v>12.29937377088294</v>
+        <v>12.31656399582418</v>
       </c>
       <c r="P16" t="n">
-        <v>385.397857315937</v>
+        <v>385.3221699134964</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36611,28 +36687,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.066454304214889</v>
+        <v>-1.058067548532111</v>
       </c>
       <c r="J17" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K17" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2722870194033392</v>
+        <v>0.2691586531597177</v>
       </c>
       <c r="M17" t="n">
-        <v>8.902674986975127</v>
+        <v>8.937538580175262</v>
       </c>
       <c r="N17" t="n">
-        <v>194.9685329754712</v>
+        <v>195.4728140888286</v>
       </c>
       <c r="O17" t="n">
-        <v>13.96311329809621</v>
+        <v>13.98115925411154</v>
       </c>
       <c r="P17" t="n">
-        <v>397.4691342108062</v>
+        <v>397.3861264155526</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36689,28 +36765,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8809736578465124</v>
+        <v>-0.8726235087294694</v>
       </c>
       <c r="J18" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K18" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3309496946332978</v>
+        <v>0.3257589075107877</v>
       </c>
       <c r="M18" t="n">
-        <v>7.811441127302251</v>
+        <v>7.834680366714253</v>
       </c>
       <c r="N18" t="n">
-        <v>100.3940948559082</v>
+        <v>101.1010812074164</v>
       </c>
       <c r="O18" t="n">
-        <v>10.01968536711149</v>
+        <v>10.05490334152529</v>
       </c>
       <c r="P18" t="n">
-        <v>404.5769331418538</v>
+        <v>404.4941069802621</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36767,28 +36843,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.010962212160989</v>
+        <v>-1.003340685542623</v>
       </c>
       <c r="J19" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K19" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4159126509521227</v>
+        <v>0.4113636314660253</v>
       </c>
       <c r="M19" t="n">
-        <v>7.418729022622125</v>
+        <v>7.446978481075978</v>
       </c>
       <c r="N19" t="n">
-        <v>91.55733896121161</v>
+        <v>92.12532962393136</v>
       </c>
       <c r="O19" t="n">
-        <v>9.568559920970952</v>
+        <v>9.598194081384861</v>
       </c>
       <c r="P19" t="n">
-        <v>403.8526844631191</v>
+        <v>403.7771783082997</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36826,7 +36902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T448"/>
+  <dimension ref="A1:T449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82279,7 +82355,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>-40.967147458164,172.1018643375767</t>
+          <t>-40.96718894665333,172.1015448054713</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -82308,6 +82384,108 @@
         </is>
       </c>
       <c r="T448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-40.97517510494682,172.10364880280278</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-40.97451492458386,172.10343769542052</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-40.97383859416107,172.10334121720004</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-40.97315299238511,172.10331052250444</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-40.97249647807331,172.1030732411239</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-40.971840401184515,172.10283280623025</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-40.97116995172028,172.10269437738577</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-40.970509681526316,172.10248362228728</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-40.9698458995425,172.10229775523146</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-40.969190519402645,172.10205218302414</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-40.968589475513525,172.10139210493583</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-40.967845810420265,172.10178668868934</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-40.96718411043098,172.10158205300195</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-40.96651791322207,172.10141221056975</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-40.96586351064605,172.10115147681424</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-40.96520694155043,172.10090737712073</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-40.9645574370086,172.10060881548037</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>-40.96388053677589,172.10052119858778</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
